--- a/research/traditional_assets/database/data/malaysia/malaysia_insurance_prop_cas.xlsx
+++ b/research/traditional_assets/database/data/malaysia/malaysia_insurance_prop_cas.xlsx
@@ -588,46 +588,46 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.0213</v>
+        <v>0.0188</v>
       </c>
       <c r="E2">
-        <v>-0.1852</v>
+        <v>0.256</v>
       </c>
       <c r="G2">
-        <v>0.2748563218390805</v>
+        <v>0.3900030506406345</v>
       </c>
       <c r="H2">
-        <v>0.2748563218390805</v>
+        <v>0.3900030506406345</v>
       </c>
       <c r="I2">
-        <v>0.2691297208538588</v>
+        <v>0.3033862111043319</v>
       </c>
       <c r="J2">
-        <v>0.1948634500220254</v>
+        <v>0.2763521142484807</v>
       </c>
       <c r="K2">
-        <v>90.021</v>
+        <v>113.7</v>
       </c>
       <c r="L2">
-        <v>0.1847721674876847</v>
+        <v>0.3468578401464307</v>
       </c>
       <c r="M2">
         <v>73.34</v>
       </c>
       <c r="N2">
-        <v>0.04514619883040936</v>
+        <v>0.05354066287049205</v>
       </c>
       <c r="O2">
-        <v>0.8146987925039714</v>
+        <v>0.6450307827616535</v>
       </c>
       <c r="P2">
         <v>73.34</v>
       </c>
       <c r="Q2">
-        <v>0.04514619883040936</v>
+        <v>0.05354066287049205</v>
       </c>
       <c r="R2">
-        <v>0.8146987925039714</v>
+        <v>0.6450307827616535</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -636,73 +636,73 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>82</v>
+        <v>185</v>
       </c>
       <c r="V2">
-        <v>0.05047706986765158</v>
+        <v>0.135056212585779</v>
       </c>
       <c r="W2">
-        <v>0.006270430906389301</v>
+        <v>0.1169865251122907</v>
       </c>
       <c r="X2">
-        <v>0.05794379259244432</v>
+        <v>0.09447079141823261</v>
       </c>
       <c r="Y2">
-        <v>-0.05167336168605502</v>
+        <v>0.02251573369405811</v>
       </c>
       <c r="Z2">
-        <v>0.6099072370150599</v>
+        <v>0.3386118772402822</v>
       </c>
       <c r="AA2">
-        <v>0.04278651086799252</v>
+        <v>0.1173294433638974</v>
       </c>
       <c r="AB2">
-        <v>0.05759640366520607</v>
+        <v>0.09406228192039606</v>
       </c>
       <c r="AC2">
-        <v>-0.01480989279721354</v>
+        <v>0.02341791761015305</v>
       </c>
       <c r="AD2">
-        <v>37.27</v>
+        <v>12.769</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>37.27</v>
+        <v>12.769</v>
       </c>
       <c r="AG2">
-        <v>-44.73</v>
+        <v>-172.231</v>
       </c>
       <c r="AH2">
-        <v>0.02242789315007492</v>
+        <v>0.009235705415064275</v>
       </c>
       <c r="AI2">
-        <v>0.03026218566545142</v>
+        <v>0.01284130941330633</v>
       </c>
       <c r="AJ2">
-        <v>-0.02831424827664786</v>
+        <v>-0.1438171829765132</v>
       </c>
       <c r="AK2">
-        <v>-0.0389102012056682</v>
+        <v>-0.2127966354036292</v>
       </c>
       <c r="AL2">
-        <v>2.081</v>
+        <v>1.309</v>
       </c>
       <c r="AM2">
-        <v>2.081</v>
+        <v>1.309</v>
       </c>
       <c r="AN2">
-        <v>0.2779061964059354</v>
+        <v>0.1252476704266798</v>
       </c>
       <c r="AO2">
-        <v>63.00816914944738</v>
+        <v>75.97402597402598</v>
       </c>
       <c r="AP2">
-        <v>-0.333532175080158</v>
+        <v>-1.689367336929868</v>
       </c>
       <c r="AQ2">
-        <v>63.00816914944738</v>
+        <v>75.97402597402598</v>
       </c>
     </row>
     <row r="3">
@@ -722,46 +722,46 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.0176</v>
+        <v>0.0243</v>
       </c>
       <c r="E3">
-        <v>-0.0434</v>
+        <v>-0.0315</v>
       </c>
       <c r="G3">
-        <v>0.3652613827993255</v>
+        <v>0.4586939417781274</v>
       </c>
       <c r="H3">
-        <v>0.3652613827993255</v>
+        <v>0.4586939417781274</v>
       </c>
       <c r="I3">
-        <v>0.3720067453625632</v>
+        <v>0.3359559402045634</v>
       </c>
       <c r="J3">
-        <v>0.2949818405813454</v>
+        <v>0.2548631270517377</v>
       </c>
       <c r="K3">
-        <v>87.7</v>
+        <v>57.3</v>
       </c>
       <c r="L3">
-        <v>0.2957841483979764</v>
+        <v>0.2254130605822187</v>
       </c>
       <c r="M3">
-        <v>69.5</v>
+        <v>60</v>
       </c>
       <c r="N3">
-        <v>0.0516959238321928</v>
+        <v>0.05218752718100374</v>
       </c>
       <c r="O3">
-        <v>0.7924743443557583</v>
+        <v>1.047120418848168</v>
       </c>
       <c r="P3">
-        <v>69.5</v>
+        <v>60</v>
       </c>
       <c r="Q3">
-        <v>0.0516959238321928</v>
+        <v>0.05218752718100374</v>
       </c>
       <c r="R3">
-        <v>0.7924743443557583</v>
+        <v>1.047120418848168</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -770,73 +770,73 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>28.7</v>
+        <v>95.5</v>
       </c>
       <c r="V3">
-        <v>0.02134781315084796</v>
+        <v>0.08306514742976429</v>
       </c>
       <c r="W3">
-        <v>0.2064015062367616</v>
+        <v>0.1169865251122907</v>
       </c>
       <c r="X3">
-        <v>0.05777488291402538</v>
+        <v>0.09447079141823261</v>
       </c>
       <c r="Y3">
-        <v>0.1486266233227362</v>
+        <v>0.02251573369405811</v>
       </c>
       <c r="Z3">
-        <v>0.7212357090732182</v>
+        <v>0.540391156462585</v>
       </c>
       <c r="AA3">
-        <v>0.2127514369554097</v>
+        <v>0.1377257799671593</v>
       </c>
       <c r="AB3">
-        <v>0.05755316685322102</v>
+        <v>0.09406228192039606</v>
       </c>
       <c r="AC3">
-        <v>0.1551982701021886</v>
+        <v>0.0436634980467632</v>
       </c>
       <c r="AD3">
-        <v>9.300000000000001</v>
+        <v>10</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>9.300000000000001</v>
+        <v>10</v>
       </c>
       <c r="AG3">
-        <v>-19.4</v>
+        <v>-85.5</v>
       </c>
       <c r="AH3">
-        <v>0.006870059836005023</v>
+        <v>0.008622919720617401</v>
       </c>
       <c r="AI3">
-        <v>0.01863354037267081</v>
+        <v>0.02185792349726776</v>
       </c>
       <c r="AJ3">
-        <v>-0.01464150943396226</v>
+        <v>-0.08034204096974253</v>
       </c>
       <c r="AK3">
-        <v>-0.04124149659863945</v>
+        <v>-0.2361878453038674</v>
       </c>
       <c r="AL3">
-        <v>0.4</v>
+        <v>0.277</v>
       </c>
       <c r="AM3">
-        <v>0.4</v>
+        <v>0.277</v>
       </c>
       <c r="AN3">
-        <v>0.08363309352517986</v>
+        <v>0.116144018583043</v>
       </c>
       <c r="AO3">
-        <v>275.75</v>
+        <v>308.3032490974729</v>
       </c>
       <c r="AP3">
-        <v>-0.1744604316546762</v>
+        <v>-0.9930313588850175</v>
       </c>
       <c r="AQ3">
-        <v>275.75</v>
+        <v>308.3032490974729</v>
       </c>
     </row>
     <row r="4">
@@ -847,7 +847,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>MPHB Capital Berhad (KLSE:MPHBCAP)</t>
+          <t>Pacific &amp; Orient Berhad (KLSE:P&amp;O)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -856,118 +856,121 @@
         </is>
       </c>
       <c r="D4">
-        <v>0.0241</v>
+        <v>0.0188</v>
       </c>
       <c r="E4">
-        <v>-0.327</v>
+        <v>0.48</v>
       </c>
       <c r="G4">
-        <v>0.1734960767218832</v>
+        <v>0.1827242524916944</v>
       </c>
       <c r="H4">
-        <v>0.1734960767218832</v>
+        <v>0.1827242524916944</v>
       </c>
       <c r="I4">
-        <v>0.1368788142981691</v>
+        <v>0.1760797342192691</v>
       </c>
       <c r="J4">
-        <v>0.1172096737561633</v>
+        <v>0.172485975709384</v>
       </c>
       <c r="K4">
-        <v>2.11</v>
+        <v>11.7</v>
       </c>
       <c r="L4">
-        <v>0.01839581517000872</v>
+        <v>0.1943521594684385</v>
       </c>
       <c r="M4">
-        <v>-0</v>
+        <v>5.65</v>
       </c>
       <c r="N4">
-        <v>-0</v>
+        <v>0.08599695585996955</v>
       </c>
       <c r="O4">
-        <v>-0</v>
+        <v>0.482905982905983</v>
       </c>
       <c r="P4">
-        <v>-0</v>
+        <v>5.65</v>
       </c>
       <c r="Q4">
-        <v>-0</v>
+        <v>0.08599695585996955</v>
       </c>
       <c r="R4">
-        <v>-0</v>
+        <v>0.482905982905983</v>
       </c>
       <c r="S4">
         <v>0</v>
       </c>
+      <c r="T4">
+        <v>0</v>
+      </c>
       <c r="U4">
-        <v>41.1</v>
+        <v>22.3</v>
       </c>
       <c r="V4">
-        <v>0.187073281747838</v>
+        <v>0.3394216133942161</v>
       </c>
       <c r="W4">
-        <v>0.006270430906389301</v>
+        <v>0.1551724137931034</v>
       </c>
       <c r="X4">
-        <v>0.05794379259244432</v>
+        <v>0.09580695109509862</v>
       </c>
       <c r="Y4">
-        <v>-0.05167336168605502</v>
+        <v>0.0593654626980048</v>
       </c>
       <c r="Z4">
-        <v>0.3650424875083543</v>
+        <v>0.6802259887005651</v>
       </c>
       <c r="AA4">
-        <v>0.04278651086799252</v>
+        <v>0.1173294433638974</v>
       </c>
       <c r="AB4">
-        <v>0.05759640366520607</v>
+        <v>0.09391152575374431</v>
       </c>
       <c r="AC4">
-        <v>-0.01480989279721354</v>
+        <v>0.02341791761015305</v>
       </c>
       <c r="AD4">
-        <v>2.67</v>
+        <v>2.66</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>2.67</v>
+        <v>2.66</v>
       </c>
       <c r="AG4">
-        <v>-38.43</v>
+        <v>-19.64</v>
       </c>
       <c r="AH4">
-        <v>0.01200701533480236</v>
+        <v>0.03891164423639556</v>
       </c>
       <c r="AI4">
-        <v>0.004414171640187148</v>
+        <v>0.02551314022635719</v>
       </c>
       <c r="AJ4">
-        <v>-0.2120041926408121</v>
+        <v>-0.4264003473729918</v>
       </c>
       <c r="AK4">
-        <v>-0.06816609610302073</v>
+        <v>-0.2396290873596877</v>
       </c>
       <c r="AL4">
-        <v>0.131</v>
+        <v>1</v>
       </c>
       <c r="AM4">
-        <v>0.131</v>
+        <v>1</v>
       </c>
       <c r="AN4">
-        <v>0.1552325581395349</v>
+        <v>0.2418181818181818</v>
       </c>
       <c r="AO4">
-        <v>119.8473282442748</v>
+        <v>10.6</v>
       </c>
       <c r="AP4">
-        <v>-2.234302325581396</v>
+        <v>-1.785454545454545</v>
       </c>
       <c r="AQ4">
-        <v>119.8473282442748</v>
+        <v>10.6</v>
       </c>
     </row>
     <row r="5">
@@ -978,7 +981,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Pacific &amp; Orient Berhad (KLSE:P&amp;O)</t>
+          <t>MPHB Capital Berhad (KLSE:MPHBCAP)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -987,43 +990,46 @@
         </is>
       </c>
       <c r="D5">
-        <v>0.0213</v>
+        <v>-0.341</v>
+      </c>
+      <c r="E5">
+        <v>0.256</v>
       </c>
       <c r="G5">
-        <v>0.07513157894736842</v>
+        <v>0.01813432835820895</v>
       </c>
       <c r="H5">
-        <v>0.07513157894736842</v>
+        <v>0.01813432835820895</v>
       </c>
       <c r="I5">
-        <v>0.06736842105263158</v>
+        <v>0.2574626865671642</v>
       </c>
       <c r="J5">
-        <v>0.03522699879469667</v>
+        <v>0.2560377743113412</v>
       </c>
       <c r="K5">
-        <v>0.211</v>
+        <v>44.7</v>
       </c>
       <c r="L5">
-        <v>0.002776315789473684</v>
+        <v>3.335820895522388</v>
       </c>
       <c r="M5">
-        <v>3.84</v>
+        <v>7.69</v>
       </c>
       <c r="N5">
-        <v>0.06357615894039735</v>
+        <v>0.04980569948186529</v>
       </c>
       <c r="O5">
-        <v>18.19905213270142</v>
+        <v>0.1720357941834452</v>
       </c>
       <c r="P5">
-        <v>3.84</v>
+        <v>7.69</v>
       </c>
       <c r="Q5">
-        <v>0.06357615894039735</v>
+        <v>0.04980569948186529</v>
       </c>
       <c r="R5">
-        <v>18.19905213270142</v>
+        <v>0.1720357941834452</v>
       </c>
       <c r="S5">
         <v>0</v>
@@ -1032,73 +1038,73 @@
         <v>0</v>
       </c>
       <c r="U5">
-        <v>12.2</v>
+        <v>67.2</v>
       </c>
       <c r="V5">
-        <v>0.2019867549668874</v>
+        <v>0.4352331606217616</v>
       </c>
       <c r="W5">
-        <v>0.003231240428790199</v>
+        <v>0.09986595174262734</v>
       </c>
       <c r="X5">
-        <v>0.07106595825940326</v>
+        <v>0.0941348736229429</v>
       </c>
       <c r="Y5">
-        <v>-0.06783471783061307</v>
+        <v>0.005731078119684443</v>
       </c>
       <c r="Z5">
-        <v>1.034013605442177</v>
+        <v>0.03274922403890803</v>
       </c>
       <c r="AA5">
-        <v>0.03642519603261152</v>
+        <v>0.008385038433345484</v>
       </c>
       <c r="AB5">
-        <v>0.05761477945959068</v>
+        <v>0.09410785524068102</v>
       </c>
       <c r="AC5">
-        <v>-0.02118958342697916</v>
+        <v>-0.08572281680733554</v>
       </c>
       <c r="AD5">
-        <v>25.3</v>
+        <v>0.109</v>
       </c>
       <c r="AE5">
         <v>0</v>
       </c>
       <c r="AF5">
-        <v>25.3</v>
+        <v>0.109</v>
       </c>
       <c r="AG5">
-        <v>13.1</v>
+        <v>-67.09100000000001</v>
       </c>
       <c r="AH5">
-        <v>0.2952158693115519</v>
+        <v>0.0007054605233352102</v>
       </c>
       <c r="AI5">
-        <v>0.1982758620689655</v>
+        <v>0.0002519596217369495</v>
       </c>
       <c r="AJ5">
-        <v>0.1782312925170068</v>
+        <v>-0.7684316622570412</v>
       </c>
       <c r="AK5">
-        <v>0.1135181975736569</v>
+        <v>-0.1836052204516036</v>
       </c>
       <c r="AL5">
-        <v>1.55</v>
+        <v>0.032</v>
       </c>
       <c r="AM5">
-        <v>1.55</v>
+        <v>0.032</v>
       </c>
       <c r="AN5">
-        <v>4.430823117338003</v>
+        <v>0.02247422680412371</v>
       </c>
       <c r="AO5">
-        <v>3.303225806451613</v>
+        <v>107.8125</v>
       </c>
       <c r="AP5">
-        <v>2.294220665499124</v>
+        <v>-13.83319587628866</v>
       </c>
       <c r="AQ5">
-        <v>3.303225806451613</v>
+        <v>107.8125</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/malaysia/malaysia_insurance_prop_cas.xlsx
+++ b/research/traditional_assets/database/data/malaysia/malaysia_insurance_prop_cas.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ5"/>
+  <dimension ref="A1:AQ4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,46 +588,46 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.0188</v>
+        <v>0.0006999999999999992</v>
       </c>
       <c r="E2">
-        <v>0.256</v>
+        <v>0.0007000000000000001</v>
       </c>
       <c r="G2">
-        <v>0.3900030506406345</v>
+        <v>0.2397919762258544</v>
       </c>
       <c r="H2">
-        <v>0.3900030506406345</v>
+        <v>0.2397919762258544</v>
       </c>
       <c r="I2">
-        <v>0.3033862111043319</v>
+        <v>0.2459732540861813</v>
       </c>
       <c r="J2">
-        <v>0.2763521142484807</v>
+        <v>0.2181057640278624</v>
       </c>
       <c r="K2">
-        <v>113.7</v>
+        <v>63.09</v>
       </c>
       <c r="L2">
-        <v>0.3468578401464307</v>
+        <v>0.1874888558692422</v>
       </c>
       <c r="M2">
-        <v>73.34</v>
+        <v>54.55</v>
       </c>
       <c r="N2">
-        <v>0.05354066287049205</v>
+        <v>0.04974920200638395</v>
       </c>
       <c r="O2">
-        <v>0.6450307827616535</v>
+        <v>0.8646378189887461</v>
       </c>
       <c r="P2">
-        <v>73.34</v>
+        <v>54.55</v>
       </c>
       <c r="Q2">
-        <v>0.05354066287049205</v>
+        <v>0.04974920200638395</v>
       </c>
       <c r="R2">
-        <v>0.6450307827616535</v>
+        <v>0.8646378189887461</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -636,73 +636,73 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>185</v>
+        <v>86.73</v>
       </c>
       <c r="V2">
-        <v>0.135056212585779</v>
+        <v>0.07909712722298222</v>
       </c>
       <c r="W2">
-        <v>0.1169865251122907</v>
+        <v>0.04944979857107881</v>
       </c>
       <c r="X2">
-        <v>0.09447079141823261</v>
+        <v>0.08313242207280019</v>
       </c>
       <c r="Y2">
-        <v>0.02251573369405811</v>
+        <v>-0.03368262350172138</v>
       </c>
       <c r="Z2">
-        <v>0.3386118772402822</v>
+        <v>0.8056792606426281</v>
       </c>
       <c r="AA2">
-        <v>0.1173294433638974</v>
+        <v>0.04464955048753225</v>
       </c>
       <c r="AB2">
-        <v>0.09406228192039606</v>
+        <v>0.08044243828944098</v>
       </c>
       <c r="AC2">
-        <v>0.02341791761015305</v>
+        <v>-0.03579288780190873</v>
       </c>
       <c r="AD2">
-        <v>12.769</v>
+        <v>16.98</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>12.769</v>
+        <v>16.98</v>
       </c>
       <c r="AG2">
-        <v>-172.231</v>
+        <v>-69.75</v>
       </c>
       <c r="AH2">
-        <v>0.009235705415064275</v>
+        <v>0.01524948809138916</v>
       </c>
       <c r="AI2">
-        <v>0.01284130941330633</v>
+        <v>0.0298586199620173</v>
       </c>
       <c r="AJ2">
-        <v>-0.1438171829765132</v>
+        <v>-0.0679327976625274</v>
       </c>
       <c r="AK2">
-        <v>-0.2127966354036292</v>
+        <v>-0.1447245564892624</v>
       </c>
       <c r="AL2">
-        <v>1.309</v>
+        <v>7.044</v>
       </c>
       <c r="AM2">
-        <v>1.309</v>
+        <v>7.044</v>
       </c>
       <c r="AN2">
-        <v>0.1252476704266798</v>
+        <v>0.2031343462136619</v>
       </c>
       <c r="AO2">
-        <v>75.97402597402598</v>
+        <v>11.75042589437819</v>
       </c>
       <c r="AP2">
-        <v>-1.689367336929868</v>
+        <v>-0.8344299557363321</v>
       </c>
       <c r="AQ2">
-        <v>75.97402597402598</v>
+        <v>11.75042589437819</v>
       </c>
     </row>
     <row r="3">
@@ -722,46 +722,46 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.0243</v>
+        <v>0.0476</v>
       </c>
       <c r="E3">
-        <v>-0.0315</v>
+        <v>0.0007000000000000001</v>
       </c>
       <c r="G3">
-        <v>0.4586939417781274</v>
+        <v>0.2888888888888889</v>
       </c>
       <c r="H3">
-        <v>0.4586939417781274</v>
+        <v>0.2888888888888889</v>
       </c>
       <c r="I3">
-        <v>0.3359559402045634</v>
+        <v>0.2973063973063973</v>
       </c>
       <c r="J3">
-        <v>0.2548631270517377</v>
+        <v>0.2299398610381269</v>
       </c>
       <c r="K3">
-        <v>57.3</v>
+        <v>66.90000000000001</v>
       </c>
       <c r="L3">
-        <v>0.2254130605822187</v>
+        <v>0.2252525252525253</v>
       </c>
       <c r="M3">
-        <v>60</v>
+        <v>51.8</v>
       </c>
       <c r="N3">
-        <v>0.05218752718100374</v>
+        <v>0.04987483150394762</v>
       </c>
       <c r="O3">
-        <v>1.047120418848168</v>
+        <v>0.7742899850523168</v>
       </c>
       <c r="P3">
-        <v>60</v>
+        <v>51.8</v>
       </c>
       <c r="Q3">
-        <v>0.05218752718100374</v>
+        <v>0.04987483150394762</v>
       </c>
       <c r="R3">
-        <v>1.047120418848168</v>
+        <v>0.7742899850523168</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -770,73 +770,73 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>95.5</v>
+        <v>78.40000000000001</v>
       </c>
       <c r="V3">
-        <v>0.08306514742976429</v>
+        <v>0.07548623146543425</v>
       </c>
       <c r="W3">
-        <v>0.1169865251122907</v>
+        <v>0.1494972067039106</v>
       </c>
       <c r="X3">
-        <v>0.09447079141823261</v>
+        <v>0.08102395107574192</v>
       </c>
       <c r="Y3">
-        <v>0.02251573369405811</v>
+        <v>0.06847325562816869</v>
       </c>
       <c r="Z3">
-        <v>0.540391156462585</v>
+        <v>0.8204419889502762</v>
       </c>
       <c r="AA3">
-        <v>0.1377257799671593</v>
+        <v>0.188652316929071</v>
       </c>
       <c r="AB3">
-        <v>0.09406228192039606</v>
+        <v>0.08071317122412305</v>
       </c>
       <c r="AC3">
-        <v>0.0436634980467632</v>
+        <v>0.1079391457049479</v>
       </c>
       <c r="AD3">
-        <v>10</v>
+        <v>8.83</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>10</v>
+        <v>8.83</v>
       </c>
       <c r="AG3">
-        <v>-85.5</v>
+        <v>-69.57000000000001</v>
       </c>
       <c r="AH3">
-        <v>0.008622919720617401</v>
+        <v>0.008430157623898496</v>
       </c>
       <c r="AI3">
-        <v>0.02185792349726776</v>
+        <v>0.01889457128795498</v>
       </c>
       <c r="AJ3">
-        <v>-0.08034204096974253</v>
+        <v>-0.07179344292746356</v>
       </c>
       <c r="AK3">
-        <v>-0.2361878453038674</v>
+        <v>-0.1788753760316767</v>
       </c>
       <c r="AL3">
-        <v>0.277</v>
+        <v>6.89</v>
       </c>
       <c r="AM3">
-        <v>0.277</v>
+        <v>6.89</v>
       </c>
       <c r="AN3">
-        <v>0.116144018583043</v>
+        <v>0.09954904171364148</v>
       </c>
       <c r="AO3">
-        <v>308.3032490974729</v>
+        <v>12.81567489114659</v>
       </c>
       <c r="AP3">
-        <v>-0.9930313588850175</v>
+        <v>-0.7843291995490418</v>
       </c>
       <c r="AQ3">
-        <v>308.3032490974729</v>
+        <v>12.81567489114659</v>
       </c>
     </row>
     <row r="4">
@@ -856,46 +856,43 @@
         </is>
       </c>
       <c r="D4">
-        <v>0.0188</v>
-      </c>
-      <c r="E4">
-        <v>0.48</v>
+        <v>-0.0462</v>
       </c>
       <c r="G4">
-        <v>0.1827242524916944</v>
+        <v>-0.1293670886075949</v>
       </c>
       <c r="H4">
-        <v>0.1827242524916944</v>
+        <v>-0.1293670886075949</v>
       </c>
       <c r="I4">
-        <v>0.1760797342192691</v>
+        <v>-0.14</v>
       </c>
       <c r="J4">
-        <v>0.172485975709384</v>
+        <v>-0.14</v>
       </c>
       <c r="K4">
-        <v>11.7</v>
+        <v>-3.81</v>
       </c>
       <c r="L4">
-        <v>0.1943521594684385</v>
+        <v>-0.09645569620253165</v>
       </c>
       <c r="M4">
-        <v>5.65</v>
+        <v>2.75</v>
       </c>
       <c r="N4">
-        <v>0.08599695585996955</v>
+        <v>0.04749568221070812</v>
       </c>
       <c r="O4">
-        <v>0.482905982905983</v>
+        <v>-0.7217847769028871</v>
       </c>
       <c r="P4">
-        <v>5.65</v>
+        <v>2.75</v>
       </c>
       <c r="Q4">
-        <v>0.08599695585996955</v>
+        <v>0.04749568221070812</v>
       </c>
       <c r="R4">
-        <v>0.482905982905983</v>
+        <v>-0.7217847769028871</v>
       </c>
       <c r="S4">
         <v>0</v>
@@ -904,207 +901,73 @@
         <v>0</v>
       </c>
       <c r="U4">
-        <v>22.3</v>
+        <v>8.33</v>
       </c>
       <c r="V4">
-        <v>0.3394216133942161</v>
+        <v>0.1438687392055268</v>
       </c>
       <c r="W4">
-        <v>0.1551724137931034</v>
+        <v>-0.05059760956175299</v>
       </c>
       <c r="X4">
-        <v>0.09580695109509862</v>
+        <v>0.08524089306985846</v>
       </c>
       <c r="Y4">
-        <v>0.0593654626980048</v>
+        <v>-0.1358385026316115</v>
       </c>
       <c r="Z4">
-        <v>0.6802259887005651</v>
+        <v>0.7096658282429034</v>
       </c>
       <c r="AA4">
-        <v>0.1173294433638974</v>
+        <v>-0.09935321595400648</v>
       </c>
       <c r="AB4">
-        <v>0.09391152575374431</v>
+        <v>0.0801717053547589</v>
       </c>
       <c r="AC4">
-        <v>0.02341791761015305</v>
+        <v>-0.1795249213087654</v>
       </c>
       <c r="AD4">
-        <v>2.66</v>
+        <v>8.15</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>2.66</v>
+        <v>8.15</v>
       </c>
       <c r="AG4">
-        <v>-19.64</v>
+        <v>-0.1799999999999997</v>
       </c>
       <c r="AH4">
-        <v>0.03891164423639556</v>
+        <v>0.1233913701741105</v>
       </c>
       <c r="AI4">
-        <v>0.02551314022635719</v>
+        <v>0.080414405525407</v>
       </c>
       <c r="AJ4">
-        <v>-0.4264003473729918</v>
+        <v>-0.003118503118503113</v>
       </c>
       <c r="AK4">
-        <v>-0.2396290873596877</v>
+        <v>-0.001935067727370455</v>
       </c>
       <c r="AL4">
-        <v>1</v>
+        <v>0.154</v>
       </c>
       <c r="AM4">
-        <v>1</v>
+        <v>0.154</v>
       </c>
       <c r="AN4">
-        <v>0.2418181818181818</v>
+        <v>-1.594911937377691</v>
       </c>
       <c r="AO4">
-        <v>10.6</v>
+        <v>-35.90909090909091</v>
       </c>
       <c r="AP4">
-        <v>-1.785454545454545</v>
+        <v>0.035225048923679</v>
       </c>
       <c r="AQ4">
-        <v>10.6</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Malaysia</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>MPHB Capital Berhad (KLSE:MPHBCAP)</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Insurance (Prop/Cas.)</t>
-        </is>
-      </c>
-      <c r="D5">
-        <v>-0.341</v>
-      </c>
-      <c r="E5">
-        <v>0.256</v>
-      </c>
-      <c r="G5">
-        <v>0.01813432835820895</v>
-      </c>
-      <c r="H5">
-        <v>0.01813432835820895</v>
-      </c>
-      <c r="I5">
-        <v>0.2574626865671642</v>
-      </c>
-      <c r="J5">
-        <v>0.2560377743113412</v>
-      </c>
-      <c r="K5">
-        <v>44.7</v>
-      </c>
-      <c r="L5">
-        <v>3.335820895522388</v>
-      </c>
-      <c r="M5">
-        <v>7.69</v>
-      </c>
-      <c r="N5">
-        <v>0.04980569948186529</v>
-      </c>
-      <c r="O5">
-        <v>0.1720357941834452</v>
-      </c>
-      <c r="P5">
-        <v>7.69</v>
-      </c>
-      <c r="Q5">
-        <v>0.04980569948186529</v>
-      </c>
-      <c r="R5">
-        <v>0.1720357941834452</v>
-      </c>
-      <c r="S5">
-        <v>0</v>
-      </c>
-      <c r="T5">
-        <v>0</v>
-      </c>
-      <c r="U5">
-        <v>67.2</v>
-      </c>
-      <c r="V5">
-        <v>0.4352331606217616</v>
-      </c>
-      <c r="W5">
-        <v>0.09986595174262734</v>
-      </c>
-      <c r="X5">
-        <v>0.0941348736229429</v>
-      </c>
-      <c r="Y5">
-        <v>0.005731078119684443</v>
-      </c>
-      <c r="Z5">
-        <v>0.03274922403890803</v>
-      </c>
-      <c r="AA5">
-        <v>0.008385038433345484</v>
-      </c>
-      <c r="AB5">
-        <v>0.09410785524068102</v>
-      </c>
-      <c r="AC5">
-        <v>-0.08572281680733554</v>
-      </c>
-      <c r="AD5">
-        <v>0.109</v>
-      </c>
-      <c r="AE5">
-        <v>0</v>
-      </c>
-      <c r="AF5">
-        <v>0.109</v>
-      </c>
-      <c r="AG5">
-        <v>-67.09100000000001</v>
-      </c>
-      <c r="AH5">
-        <v>0.0007054605233352102</v>
-      </c>
-      <c r="AI5">
-        <v>0.0002519596217369495</v>
-      </c>
-      <c r="AJ5">
-        <v>-0.7684316622570412</v>
-      </c>
-      <c r="AK5">
-        <v>-0.1836052204516036</v>
-      </c>
-      <c r="AL5">
-        <v>0.032</v>
-      </c>
-      <c r="AM5">
-        <v>0.032</v>
-      </c>
-      <c r="AN5">
-        <v>0.02247422680412371</v>
-      </c>
-      <c r="AO5">
-        <v>107.8125</v>
-      </c>
-      <c r="AP5">
-        <v>-13.83319587628866</v>
-      </c>
-      <c r="AQ5">
-        <v>107.8125</v>
+        <v>-35.90909090909091</v>
       </c>
     </row>
   </sheetData>
